--- a/tools/importer/reports/import-procedure-detail.report.xlsx
+++ b/tools/importer/reports/import-procedure-detail.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="59">
   <si>
     <t>_reportFile</t>
   </si>
@@ -43,10 +43,52 @@
     <t>url</t>
   </si>
   <si>
+    <t>fragments/stroke-awareness-related-links.report.json</t>
+  </si>
+  <si>
+    <t>["columns-related-links"]</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>fragments/stroke-awareness-related-links</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>sa-related-links-fragment</t>
+  </si>
+  <si>
+    <t>2026-08-28T11:11:32.136Z</t>
+  </si>
+  <si>
+    <t>Stroke Awareness Related Links (fragment)</t>
+  </si>
+  <si>
+    <t>https://patients.stryker.com/ww/en/stroke-awareness/resources.html</t>
+  </si>
+  <si>
+    <t>ww/en/stroke-awareness/resources.report.json</t>
+  </si>
+  <si>
+    <t>["hero","panel","cards-brochure","cards-brochure","fragment"]</t>
+  </si>
+  <si>
+    <t>ww/en/stroke-awareness/resources</t>
+  </si>
+  <si>
+    <t>sa-resources</t>
+  </si>
+  <si>
+    <t>2026-08-28T11:11:23.677Z</t>
+  </si>
+  <si>
+    <t>Stroke Awareness Resources | Stryker</t>
+  </si>
+  <si>
     <t>us/en/ivs/treatments/balloon-kyphoplasty.html.report.json</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>CustomImportScript.default not found after 10s. The bundled script may not have loaded correctly. Check browser console for errors.</t>
@@ -80,16 +122,76 @@
     <t>us/en/ivs/treatments/balloon-kyphoplasty</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>procedure-detail</t>
   </si>
   <si>
-    <t>2026-09-01T15:48:07.041Z</t>
+    <t>2026-09-07T19:24:14.329Z</t>
   </si>
   <si>
     <t>Balloon kyphoplasty | Interventional Spine | Stryker</t>
+  </si>
+  <si>
+    <t>us/en/ivs/treatments/disc-decompression.report.json</t>
+  </si>
+  <si>
+    <t>us/en/ivs/treatments/disc-decompression</t>
+  </si>
+  <si>
+    <t>2026-09-07T19:24:41.528Z</t>
+  </si>
+  <si>
+    <t>Disc decompression | Interventional Spine | Stryker</t>
+  </si>
+  <si>
+    <t>https://patients.stryker.com/us/en/ivs/treatments/disc-decompression.html</t>
+  </si>
+  <si>
+    <t>us/en/ivs/treatments/radiofrequency-ablation.report.json</t>
+  </si>
+  <si>
+    <t>us/en/ivs/treatments/radiofrequency-ablation</t>
+  </si>
+  <si>
+    <t>2026-09-07T19:25:10.629Z</t>
+  </si>
+  <si>
+    <t>Radiofrequency ablation | Interventional Spine | Stryker</t>
+  </si>
+  <si>
+    <t>https://patients.stryker.com/us/en/ivs/treatments/radiofrequency-ablation.html</t>
+  </si>
+  <si>
+    <t>us/en/ivs/treatments/spinejack-system.report.json</t>
+  </si>
+  <si>
+    <t>us/en/ivs/treatments/spinejack-system</t>
+  </si>
+  <si>
+    <t>2026-09-07T19:24:56.083Z</t>
+  </si>
+  <si>
+    <t>SpineJack system | Interventional Spine | Stryker</t>
+  </si>
+  <si>
+    <t>https://patients.stryker.com/us/en/ivs/treatments/spinejack-system.html</t>
+  </si>
+  <si>
+    <t>us/en/ivs/treatments/vertebroplasty.report.json</t>
+  </si>
+  <si>
+    <t>["hero","panel-cta","panel-dark","panel-dark","cards","panel-gold","cards-resources"]</t>
+  </si>
+  <si>
+    <t>us/en/ivs/treatments/vertebroplasty</t>
+  </si>
+  <si>
+    <t>2026-09-07T19:24:27.527Z</t>
+  </si>
+  <si>
+    <t>Vertebroplasty | Interventional Spine | Stryker</t>
+  </si>
+  <si>
+    <t>https://patients.stryker.com/us/en/ivs/treatments/vertebroplasty.html</t>
   </si>
 </sst>
 </file>
@@ -478,12 +580,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="50" customWidth="1"/>
     <col min="5" max="5" width="47" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="7" max="7" width="27" customWidth="1"/>
     <col min="8" max="8" width="26" customWidth="1"/>
     <col min="9" max="10" width="50" customWidth="1"/>
   </cols>
@@ -531,45 +633,45 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>15</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
         <v>22</v>
@@ -581,7 +683,199 @@
         <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" t="s">
+        <v>56</v>
+      </c>
+      <c r="I9" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-procedure-detail.report.xlsx
+++ b/tools/importer/reports/import-procedure-detail.report.xlsx
@@ -125,7 +125,7 @@
     <t>procedure-detail</t>
   </si>
   <si>
-    <t>2026-09-07T19:24:14.329Z</t>
+    <t>2026-09-08T07:04:54.087Z</t>
   </si>
   <si>
     <t>Balloon kyphoplasty | Interventional Spine | Stryker</t>
@@ -137,7 +137,7 @@
     <t>us/en/ivs/treatments/disc-decompression</t>
   </si>
   <si>
-    <t>2026-09-07T19:24:41.528Z</t>
+    <t>2026-09-08T07:05:23.483Z</t>
   </si>
   <si>
     <t>Disc decompression | Interventional Spine | Stryker</t>
@@ -152,7 +152,7 @@
     <t>us/en/ivs/treatments/radiofrequency-ablation</t>
   </si>
   <si>
-    <t>2026-09-07T19:25:10.629Z</t>
+    <t>2026-09-08T07:05:53.479Z</t>
   </si>
   <si>
     <t>Radiofrequency ablation | Interventional Spine | Stryker</t>
@@ -167,7 +167,7 @@
     <t>us/en/ivs/treatments/spinejack-system</t>
   </si>
   <si>
-    <t>2026-09-07T19:24:56.083Z</t>
+    <t>2026-09-08T07:05:38.226Z</t>
   </si>
   <si>
     <t>SpineJack system | Interventional Spine | Stryker</t>
@@ -185,7 +185,7 @@
     <t>us/en/ivs/treatments/vertebroplasty</t>
   </si>
   <si>
-    <t>2026-09-07T19:24:27.527Z</t>
+    <t>2026-09-08T07:05:08.125Z</t>
   </si>
   <si>
     <t>Vertebroplasty | Interventional Spine | Stryker</t>

--- a/tools/importer/reports/import-procedure-detail.report.xlsx
+++ b/tools/importer/reports/import-procedure-detail.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="70">
   <si>
     <t>_reportFile</t>
   </si>
@@ -131,6 +131,21 @@
     <t>Balloon kyphoplasty | Interventional Spine | Stryker</t>
   </si>
   <si>
+    <t>us/en/ivs/treatments/bone-tumor-ablation.report.json</t>
+  </si>
+  <si>
+    <t>us/en/ivs/treatments/bone-tumor-ablation</t>
+  </si>
+  <si>
+    <t>2026-09-09T09:44:37.928Z</t>
+  </si>
+  <si>
+    <t>Bone tumor ablation | Interventional Spine | Stryker</t>
+  </si>
+  <si>
+    <t>https://patients.stryker.com/us/en/ivs/treatments/bone-tumor-ablation.html</t>
+  </si>
+  <si>
     <t>us/en/ivs/treatments/disc-decompression.report.json</t>
   </si>
   <si>
@@ -152,13 +167,31 @@
     <t>us/en/ivs/treatments/radiofrequency-ablation</t>
   </si>
   <si>
-    <t>2026-09-08T07:05:53.479Z</t>
+    <t>2026-09-09T08:18:43.313Z</t>
   </si>
   <si>
     <t>Radiofrequency ablation | Interventional Spine | Stryker</t>
   </si>
   <si>
     <t>https://patients.stryker.com/us/en/ivs/treatments/radiofrequency-ablation.html</t>
+  </si>
+  <si>
+    <t>us/en/ivs/treatments/sacroplasty.report.json</t>
+  </si>
+  <si>
+    <t>["hero","panel-cta","panel-dark","panel-dark","cards","panel-gold"]</t>
+  </si>
+  <si>
+    <t>us/en/ivs/treatments/sacroplasty</t>
+  </si>
+  <si>
+    <t>2026-09-09T09:44:53.028Z</t>
+  </si>
+  <si>
+    <t>Sacroplasty | Interventional Spine | Stryker</t>
+  </si>
+  <si>
+    <t>https://patients.stryker.com/us/en/ivs/treatments/sacroplasty.html</t>
   </si>
   <si>
     <t>us/en/ivs/treatments/spinejack-system.report.json</t>
@@ -580,7 +613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="50" customWidth="1"/>
@@ -878,6 +911,70 @@
         <v>58</v>
       </c>
     </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" t="s">
+        <v>61</v>
+      </c>
+      <c r="I10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" t="s">
+        <v>68</v>
+      </c>
+      <c r="J11" t="s">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tools/importer/reports/import-procedure-detail.report.xlsx
+++ b/tools/importer/reports/import-procedure-detail.report.xlsx
@@ -185,7 +185,7 @@
     <t>us/en/ivs/treatments/sacroplasty</t>
   </si>
   <si>
-    <t>2026-09-09T09:44:53.028Z</t>
+    <t>2026-09-09T10:28:33.905Z</t>
   </si>
   <si>
     <t>Sacroplasty | Interventional Spine | Stryker</t>

--- a/tools/importer/reports/import-procedure-detail.report.xlsx
+++ b/tools/importer/reports/import-procedure-detail.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="78">
   <si>
     <t>_reportFile</t>
   </si>
@@ -125,7 +125,7 @@
     <t>procedure-detail</t>
   </si>
   <si>
-    <t>2026-09-08T07:04:54.087Z</t>
+    <t>2026-09-09T12:46:56.430Z</t>
   </si>
   <si>
     <t>Balloon kyphoplasty | Interventional Spine | Stryker</t>
@@ -137,7 +137,7 @@
     <t>us/en/ivs/treatments/bone-tumor-ablation</t>
   </si>
   <si>
-    <t>2026-09-09T09:44:37.928Z</t>
+    <t>2026-09-09T12:48:17.527Z</t>
   </si>
   <si>
     <t>Bone tumor ablation | Interventional Spine | Stryker</t>
@@ -146,28 +146,45 @@
     <t>https://patients.stryker.com/us/en/ivs/treatments/bone-tumor-ablation.html</t>
   </si>
   <si>
+    <t>us/en/ivs/treatments/disc-decompression.html.report.json</t>
+  </si>
+  <si>
+    <t>page.goto: Target page, context or browser has been closed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page.goto: Target page, context or browser has been closed
+    at processUrl (/home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:597:20)
+    at async main (/home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:954:22)</t>
+  </si>
+  <si>
+    <t>us/en/ivs/treatments/disc-decompression.html</t>
+  </si>
+  <si>
+    <t>2026-09-09T12:46:29.133Z</t>
+  </si>
+  <si>
+    <t>https://patients.stryker.com/us/en/ivs/treatments/disc-decompression.html</t>
+  </si>
+  <si>
     <t>us/en/ivs/treatments/disc-decompression.report.json</t>
   </si>
   <si>
     <t>us/en/ivs/treatments/disc-decompression</t>
   </si>
   <si>
-    <t>2026-09-08T07:05:23.483Z</t>
+    <t>2026-09-09T12:47:27.426Z</t>
   </si>
   <si>
     <t>Disc decompression | Interventional Spine | Stryker</t>
   </si>
   <si>
-    <t>https://patients.stryker.com/us/en/ivs/treatments/disc-decompression.html</t>
-  </si>
-  <si>
     <t>us/en/ivs/treatments/radiofrequency-ablation.report.json</t>
   </si>
   <si>
     <t>us/en/ivs/treatments/radiofrequency-ablation</t>
   </si>
   <si>
-    <t>2026-09-09T08:18:43.313Z</t>
+    <t>2026-09-09T12:47:59.226Z</t>
   </si>
   <si>
     <t>Radiofrequency ablation | Interventional Spine | Stryker</t>
@@ -176,6 +193,18 @@
     <t>https://patients.stryker.com/us/en/ivs/treatments/radiofrequency-ablation.html</t>
   </si>
   <si>
+    <t>us/en/ivs/treatments/sacroplasty.html.report.json</t>
+  </si>
+  <si>
+    <t>us/en/ivs/treatments/sacroplasty.html</t>
+  </si>
+  <si>
+    <t>2026-09-09T12:44:23.337Z</t>
+  </si>
+  <si>
+    <t>https://patients.stryker.com/us/en/ivs/treatments/sacroplasty.html</t>
+  </si>
+  <si>
     <t>us/en/ivs/treatments/sacroplasty.report.json</t>
   </si>
   <si>
@@ -185,22 +214,19 @@
     <t>us/en/ivs/treatments/sacroplasty</t>
   </si>
   <si>
-    <t>2026-09-09T10:28:33.905Z</t>
+    <t>2026-09-09T12:48:33.930Z</t>
   </si>
   <si>
     <t>Sacroplasty | Interventional Spine | Stryker</t>
   </si>
   <si>
-    <t>https://patients.stryker.com/us/en/ivs/treatments/sacroplasty.html</t>
-  </si>
-  <si>
     <t>us/en/ivs/treatments/spinejack-system.report.json</t>
   </si>
   <si>
     <t>us/en/ivs/treatments/spinejack-system</t>
   </si>
   <si>
-    <t>2026-09-08T07:05:38.226Z</t>
+    <t>2026-09-09T12:47:42.626Z</t>
   </si>
   <si>
     <t>SpineJack system | Interventional Spine | Stryker</t>
@@ -218,7 +244,7 @@
     <t>us/en/ivs/treatments/vertebroplasty</t>
   </si>
   <si>
-    <t>2026-09-08T07:05:08.125Z</t>
+    <t>2026-09-09T12:47:11.905Z</t>
   </si>
   <si>
     <t>Vertebroplasty | Interventional Spine | Stryker</t>
@@ -613,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="50" customWidth="1"/>
@@ -820,36 +846,36 @@
         <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="H7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I7" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="J7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
         <v>33</v>
@@ -861,7 +887,7 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F8" t="s">
         <v>14</v>
@@ -870,13 +896,13 @@
         <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -884,16 +910,16 @@
         <v>53</v>
       </c>
       <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
         <v>54</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" t="s">
-        <v>55</v>
       </c>
       <c r="F9" t="s">
         <v>14</v>
@@ -902,62 +928,62 @@
         <v>35</v>
       </c>
       <c r="H9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9" t="s">
         <v>56</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>57</v>
-      </c>
-      <c r="J9" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" t="s">
         <v>59</v>
       </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" t="s">
         <v>60</v>
       </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" t="s">
         <v>61</v>
-      </c>
-      <c r="I10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J10" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
         <v>64</v>
-      </c>
-      <c r="B11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" t="s">
-        <v>66</v>
       </c>
       <c r="F11" t="s">
         <v>14</v>
@@ -966,13 +992,77 @@
         <v>35</v>
       </c>
       <c r="H11" t="s">
+        <v>65</v>
+      </c>
+      <c r="I11" t="s">
+        <v>66</v>
+      </c>
+      <c r="J11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>67</v>
       </c>
-      <c r="I11" t="s">
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
         <v>68</v>
       </c>
-      <c r="J11" t="s">
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" t="s">
         <v>69</v>
+      </c>
+      <c r="I12" t="s">
+        <v>70</v>
+      </c>
+      <c r="J12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" t="s">
+        <v>76</v>
+      </c>
+      <c r="J13" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-procedure-detail.report.xlsx
+++ b/tools/importer/reports/import-procedure-detail.report.xlsx
@@ -125,7 +125,7 @@
     <t>procedure-detail</t>
   </si>
   <si>
-    <t>2026-09-09T12:46:56.430Z</t>
+    <t>2026-09-09T13:53:35.305Z</t>
   </si>
   <si>
     <t>Balloon kyphoplasty | Interventional Spine | Stryker</t>
@@ -137,7 +137,7 @@
     <t>us/en/ivs/treatments/bone-tumor-ablation</t>
   </si>
   <si>
-    <t>2026-09-09T12:48:17.527Z</t>
+    <t>2026-09-09T13:57:16.429Z</t>
   </si>
   <si>
     <t>Bone tumor ablation | Interventional Spine | Stryker</t>
@@ -172,7 +172,7 @@
     <t>us/en/ivs/treatments/disc-decompression</t>
   </si>
   <si>
-    <t>2026-09-09T12:47:27.426Z</t>
+    <t>2026-09-09T13:55:38.426Z</t>
   </si>
   <si>
     <t>Disc decompression | Interventional Spine | Stryker</t>
@@ -184,7 +184,7 @@
     <t>us/en/ivs/treatments/radiofrequency-ablation</t>
   </si>
   <si>
-    <t>2026-09-09T12:47:59.226Z</t>
+    <t>2026-09-09T13:56:58.305Z</t>
   </si>
   <si>
     <t>Radiofrequency ablation | Interventional Spine | Stryker</t>
@@ -214,7 +214,7 @@
     <t>us/en/ivs/treatments/sacroplasty</t>
   </si>
   <si>
-    <t>2026-09-09T12:48:33.930Z</t>
+    <t>2026-09-09T13:57:32.425Z</t>
   </si>
   <si>
     <t>Sacroplasty | Interventional Spine | Stryker</t>
@@ -226,7 +226,7 @@
     <t>us/en/ivs/treatments/spinejack-system</t>
   </si>
   <si>
-    <t>2026-09-09T12:47:42.626Z</t>
+    <t>2026-09-09T13:56:41.425Z</t>
   </si>
   <si>
     <t>SpineJack system | Interventional Spine | Stryker</t>
@@ -244,7 +244,7 @@
     <t>us/en/ivs/treatments/vertebroplasty</t>
   </si>
   <si>
-    <t>2026-09-09T12:47:11.905Z</t>
+    <t>2026-09-09T13:54:37.030Z</t>
   </si>
   <si>
     <t>Vertebroplasty | Interventional Spine | Stryker</t>

--- a/tools/importer/reports/import-procedure-detail.report.xlsx
+++ b/tools/importer/reports/import-procedure-detail.report.xlsx
@@ -125,7 +125,7 @@
     <t>procedure-detail</t>
   </si>
   <si>
-    <t>2026-09-09T13:53:35.305Z</t>
+    <t>2026-09-09T15:12:55.431Z</t>
   </si>
   <si>
     <t>Balloon kyphoplasty | Interventional Spine | Stryker</t>
@@ -137,7 +137,7 @@
     <t>us/en/ivs/treatments/bone-tumor-ablation</t>
   </si>
   <si>
-    <t>2026-09-09T13:57:16.429Z</t>
+    <t>2026-09-09T15:14:17.823Z</t>
   </si>
   <si>
     <t>Bone tumor ablation | Interventional Spine | Stryker</t>
@@ -172,7 +172,7 @@
     <t>us/en/ivs/treatments/disc-decompression</t>
   </si>
   <si>
-    <t>2026-09-09T13:55:38.426Z</t>
+    <t>2026-09-09T15:13:30.729Z</t>
   </si>
   <si>
     <t>Disc decompression | Interventional Spine | Stryker</t>
@@ -184,7 +184,7 @@
     <t>us/en/ivs/treatments/radiofrequency-ablation</t>
   </si>
   <si>
-    <t>2026-09-09T13:56:58.305Z</t>
+    <t>2026-09-09T15:14:01.628Z</t>
   </si>
   <si>
     <t>Radiofrequency ablation | Interventional Spine | Stryker</t>
@@ -214,7 +214,7 @@
     <t>us/en/ivs/treatments/sacroplasty</t>
   </si>
   <si>
-    <t>2026-09-09T13:57:32.425Z</t>
+    <t>2026-09-09T15:14:34.201Z</t>
   </si>
   <si>
     <t>Sacroplasty | Interventional Spine | Stryker</t>
@@ -226,7 +226,7 @@
     <t>us/en/ivs/treatments/spinejack-system</t>
   </si>
   <si>
-    <t>2026-09-09T13:56:41.425Z</t>
+    <t>2026-09-09T15:13:45.928Z</t>
   </si>
   <si>
     <t>SpineJack system | Interventional Spine | Stryker</t>
@@ -244,7 +244,7 @@
     <t>us/en/ivs/treatments/vertebroplasty</t>
   </si>
   <si>
-    <t>2026-09-09T13:54:37.030Z</t>
+    <t>2026-09-09T15:13:12.533Z</t>
   </si>
   <si>
     <t>Vertebroplasty | Interventional Spine | Stryker</t>

--- a/tools/importer/reports/import-procedure-detail.report.xlsx
+++ b/tools/importer/reports/import-procedure-detail.report.xlsx
@@ -125,7 +125,7 @@
     <t>procedure-detail</t>
   </si>
   <si>
-    <t>2026-09-09T15:12:55.431Z</t>
+    <t>2026-09-10T08:33:56.134Z</t>
   </si>
   <si>
     <t>Balloon kyphoplasty | Interventional Spine | Stryker</t>
@@ -137,7 +137,7 @@
     <t>us/en/ivs/treatments/bone-tumor-ablation</t>
   </si>
   <si>
-    <t>2026-09-09T15:14:17.823Z</t>
+    <t>2026-09-10T08:39:05.525Z</t>
   </si>
   <si>
     <t>Bone tumor ablation | Interventional Spine | Stryker</t>
@@ -172,7 +172,7 @@
     <t>us/en/ivs/treatments/disc-decompression</t>
   </si>
   <si>
-    <t>2026-09-09T15:13:30.729Z</t>
+    <t>2026-09-10T08:36:00.526Z</t>
   </si>
   <si>
     <t>Disc decompression | Interventional Spine | Stryker</t>
@@ -184,7 +184,7 @@
     <t>us/en/ivs/treatments/radiofrequency-ablation</t>
   </si>
   <si>
-    <t>2026-09-09T15:14:01.628Z</t>
+    <t>2026-09-10T08:38:03.526Z</t>
   </si>
   <si>
     <t>Radiofrequency ablation | Interventional Spine | Stryker</t>
@@ -214,7 +214,7 @@
     <t>us/en/ivs/treatments/sacroplasty</t>
   </si>
   <si>
-    <t>2026-09-09T15:14:34.201Z</t>
+    <t>2026-09-10T08:40:06.327Z</t>
   </si>
   <si>
     <t>Sacroplasty | Interventional Spine | Stryker</t>
@@ -226,7 +226,7 @@
     <t>us/en/ivs/treatments/spinejack-system</t>
   </si>
   <si>
-    <t>2026-09-09T15:13:45.928Z</t>
+    <t>2026-09-10T08:37:03.028Z</t>
   </si>
   <si>
     <t>SpineJack system | Interventional Spine | Stryker</t>
@@ -244,7 +244,7 @@
     <t>us/en/ivs/treatments/vertebroplasty</t>
   </si>
   <si>
-    <t>2026-09-09T15:13:12.533Z</t>
+    <t>2026-09-10T08:34:58.326Z</t>
   </si>
   <si>
     <t>Vertebroplasty | Interventional Spine | Stryker</t>
